--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104598_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104598_W16.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6739</v>
+        <v>2.2354</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8361</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8378</v>
+        <v>1.3106</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.8815</v>
+        <v>1.8406</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.3115</v>
+        <v>0.6979</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.57</v>
+        <v>1.1427</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.8967</v>
+        <v>2.0679</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.3662</v>
+        <v>0.9136</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5306</v>
+        <v>1.1543</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9848</v>
+        <v>-0.2273</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9453</v>
+        <v>-0.2157</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0395</v>
+        <v>-0.0116</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4952</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9429</v>
+        <v>0.1672</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4548</v>
+        <v>-0.0049</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4881</v>
+        <v>0.1721</v>
       </c>
       <c r="V2" t="n">
-        <v>3.1173</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3947</v>
+        <v>1.7694</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1007</v>
+        <v>0.1244</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2939</v>
+        <v>1.645</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8351</v>
+        <v>2.0957</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6969</v>
+        <v>4.2375</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1382</v>
+        <v>-2.1418</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0746</v>
+        <v>4.4711</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9177999999999999</v>
+        <v>5.574</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1568</v>
+        <v>-1.1029</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2395</v>
+        <v>-2.3754</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2209</v>
+        <v>-1.3365</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0186</v>
+        <v>-1.0389</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3327</v>
+        <v>0.7224</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1603</v>
+        <v>-0.1097</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1724</v>
+        <v>0.832</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LIMA</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9642</v>
+        <v>1.6736</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4462</v>
+        <v>0.9261</v>
       </c>
       <c r="F4" t="n">
-        <v>0.518</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4208</v>
+        <v>-4.8886</v>
       </c>
       <c r="H4" t="n">
-        <v>0.658</v>
+        <v>-3.317</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2372</v>
+        <v>-1.5716</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8685</v>
+        <v>-2.9272</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8312</v>
+        <v>-2.3829</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>-0.5443</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4477</v>
+        <v>-1.9613</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1732</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2745</v>
+        <v>-1.0273</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8629</v>
+        <v>0.9476</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5777</v>
+        <v>0.5849</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2852</v>
+        <v>0.3627</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.1107</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>A. LIMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3313</v>
+        <v>1.4723</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7224</v>
+        <v>1.0411</v>
       </c>
       <c r="F5" t="n">
-        <v>0.609</v>
+        <v>0.4313</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1768</v>
+        <v>0.4213</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0479</v>
+        <v>0.655</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8711</v>
+        <v>-0.2337</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1615</v>
+        <v>0.8646</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8359</v>
+        <v>0.8274</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6744</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9848</v>
+        <v>-0.4433</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.788</v>
+        <v>-0.1724</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1967</v>
+        <v>-0.271</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>0.767</v>
+        <v>0.3681</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6684</v>
+        <v>0.1765</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1917</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2955</v>
+        <v>1.3263</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2967</v>
+        <v>0.6187</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5921</v>
+        <v>0.7076</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1101</v>
+        <v>-0.1192</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2585</v>
+        <v>-0.4337</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1484</v>
+        <v>0.3145</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5234</v>
+        <v>0.408</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6137</v>
+        <v>-0.0312</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.0903</v>
+        <v>0.4392</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4133</v>
+        <v>-0.5271</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3552</v>
+        <v>-0.4025</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0581</v>
+        <v>-0.1246</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9488</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2268</v>
+        <v>-0.0569</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6049</v>
+        <v>-0.1048</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8317</v>
+        <v>0.0479</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>-0.7739</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2249</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5810999999999999</v>
+        <v>1.0406</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2782</v>
+        <v>0.2747</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.7659</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1414</v>
+        <v>0.1629</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1732</v>
+        <v>2.026</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3145</v>
+        <v>-1.8632</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1242</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.8021</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1414</v>
+        <v>-1.9613</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1732</v>
+        <v>-0.7761</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3145</v>
+        <v>-1.1852</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0139</v>
+        <v>0.4923</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2782</v>
+        <v>0.2691</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2643</v>
+        <v>0.2232</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4995</v>
+        <v>0.4593</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0231</v>
+        <v>-0.2788</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5225</v>
+        <v>0.7382</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1251</v>
+        <v>0.1435</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4343</v>
+        <v>-0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3092</v>
+        <v>0.3159</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4207</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0244</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4451</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5458</v>
+        <v>0.1435</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4099</v>
+        <v>-0.1724</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1359</v>
+        <v>0.3159</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8726</v>
+        <v>-0.1394</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>-0.2788</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1074</v>
+        <v>0.1394</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1014</v>
+        <v>-0.3282</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5617</v>
+        <v>0.3111</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6631</v>
+        <v>-0.6393</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0008</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3549</v>
+        <v>-0.3615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4014</v>
+        <v>0.3857</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4014</v>
+        <v>0.3857</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4017</v>
+        <v>-0.3865</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6986</v>
+        <v>0.4645</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1603</v>
+        <v>-0.0746</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5383</v>
+        <v>0.5391</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.049</v>
+        <v>-3.2839</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9335</v>
+        <v>-3.2948</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1155</v>
+        <v>0.0109</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.1944</v>
+        <v>-5.1897</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0491</v>
+        <v>-2.0451</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.1453</v>
+        <v>-3.1445</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8901</v>
+        <v>-2.9112</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5683</v>
+        <v>-0.5795</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3043</v>
+        <v>-2.2784</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2156</v>
+        <v>0.54</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0434</v>
+        <v>-0.3836</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8278</v>
+        <v>0.9236</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2449</v>
+        <v>-3.57</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0109</v>
+        <v>-2.4013</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.234</v>
+        <v>-1.1687</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2608</v>
+        <v>-3.283</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6375</v>
+        <v>-1.6562</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6233</v>
+        <v>-1.6268</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9724</v>
+        <v>-1.019</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3299</v>
+        <v>-0.3629</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6425</v>
+        <v>-0.656</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2884</v>
+        <v>-2.264</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1183</v>
+        <v>0.5748</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9043</v>
+        <v>-0.2442</v>
       </c>
       <c r="U11" t="n">
-        <v>0.786</v>
+        <v>0.819</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7966</v>
+        <v>-4.5546</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0319</v>
+        <v>-5.7631</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2353</v>
+        <v>1.2086</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6472</v>
+        <v>-3.6381</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6379</v>
+        <v>-0.6322</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0094</v>
+        <v>-3.0059</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9452</v>
+        <v>-1.9637</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3392</v>
+        <v>0.3308</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.702</v>
+        <v>-1.6744</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4119</v>
+        <v>0.6573</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2571</v>
+        <v>0.0507</v>
       </c>
       <c r="U12" t="n">
-        <v>0.669</v>
+        <v>0.6066</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.451700000000001</v>
+        <v>-1.7598</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.9072</v>
+        <v>-7.516999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.455400000000001</v>
+        <v>5.7576</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.4251</v>
+        <v>-12.4554</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9371000000000006</v>
+        <v>-1.0017</v>
       </c>
       <c r="I13" t="n">
-        <v>-11.4882</v>
+        <v>-11.4536</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7457</v>
+        <v>1.500399999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>7.650399999999999</v>
+        <v>7.477099999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.9048</v>
+        <v>-5.9766</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.1709</v>
+        <v>-13.9555</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.587299999999999</v>
+        <v>-8.4785</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.5835</v>
+        <v>-5.477</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5367</v>
+        <v>4.5526</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6101</v>
+        <v>-13.6579</v>
       </c>
       <c r="R13" t="n">
-        <v>18.1467</v>
+        <v>18.2105</v>
       </c>
       <c r="S13" t="n">
-        <v>4.022399999999999</v>
+        <v>4.737900000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8315999999999999</v>
+        <v>-0.1194000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>4.854000000000001</v>
+        <v>4.8573</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4141</v>
+        <v>1.4051</v>
       </c>
       <c r="W13" t="n">
-        <v>4.7886</v>
+        <v>4.7597</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.3746</v>
+        <v>-3.3548</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.4641</v>
+        <v>7.1221</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7125</v>
+        <v>2.7362</v>
       </c>
       <c r="F14" t="n">
-        <v>4.7516</v>
+        <v>4.386</v>
       </c>
       <c r="G14" t="n">
-        <v>4.6157</v>
+        <v>4.6195</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1572</v>
+        <v>4.156</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4585</v>
+        <v>0.4635</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8387</v>
+        <v>3.8147</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3638</v>
+        <v>4.3437</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5251</v>
+        <v>-0.529</v>
       </c>
       <c r="M14" t="n">
-        <v>0.777</v>
+        <v>0.8048</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2066</v>
+        <v>-0.1877</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0999</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6866</v>
+        <v>-0.2559</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4133</v>
+        <v>1.0074</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8293</v>
+        <v>6.2349</v>
       </c>
       <c r="E15" t="n">
-        <v>2.269</v>
+        <v>2.4865</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5603</v>
+        <v>3.7484</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6816</v>
+        <v>3.6896</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7761</v>
+        <v>0.7864</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9054</v>
+        <v>2.9032</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1714</v>
+        <v>3.1573</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2363</v>
+        <v>2.2265</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5102</v>
+        <v>0.5322</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1225</v>
+        <v>0.2706</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6775</v>
+        <v>-0.4416</v>
       </c>
       <c r="U15" t="n">
-        <v>0.555</v>
+        <v>0.7123</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8791</v>
+        <v>3.0341</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1059</v>
+        <v>1.3185</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7732</v>
+        <v>1.7156</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9947</v>
+        <v>4.0082</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3851</v>
+        <v>1.3953</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6096</v>
+        <v>2.6129</v>
       </c>
       <c r="J16" t="n">
-        <v>4.209</v>
+        <v>4.1943</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2685</v>
+        <v>2.258</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9405</v>
+        <v>1.9363</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2143</v>
+        <v>-0.1861</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8834</v>
+        <v>-0.8628</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5012</v>
+        <v>-0.3611</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8347</v>
+        <v>-0.5995</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3336</v>
+        <v>0.2385</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3956</v>
+        <v>0.458</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4352</v>
+        <v>-0.461</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8308</v>
+        <v>0.9191</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7147</v>
+        <v>0.7089</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8499</v>
+        <v>-0.8474</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5646</v>
+        <v>1.5563</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4177</v>
+        <v>0.3939</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3605</v>
+        <v>-0.3727</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.297</v>
+        <v>0.3149</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3605</v>
+        <v>-0.2995</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6261</v>
+        <v>-0.6273</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2655</v>
+        <v>0.3278</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2883</v>
+        <v>0.3739</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6107</v>
+        <v>-1.5656</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8989</v>
+        <v>1.9395</v>
       </c>
       <c r="G18" t="n">
-        <v>7.3844</v>
+        <v>7.3701</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9652</v>
+        <v>2.9722</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4193</v>
+        <v>4.3979</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2842</v>
+        <v>7.2404</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3768</v>
+        <v>3.3612</v>
       </c>
       <c r="L18" t="n">
-        <v>3.9074</v>
+        <v>3.8792</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1002</v>
+        <v>0.1297</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4116</v>
+        <v>-0.389</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.444</v>
+        <v>-5.4632</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.9391</v>
+        <v>-7.9671</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5595</v>
+        <v>-0.4436</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9557</v>
+        <v>-0.8389</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3962</v>
+        <v>0.3953</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2305</v>
+        <v>0.3253</v>
       </c>
       <c r="E19" t="n">
-        <v>0.41</v>
+        <v>0.5179</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1795</v>
+        <v>-0.1926</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3475</v>
+        <v>-0.3412</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1456</v>
+        <v>0.1519</v>
       </c>
       <c r="I19" t="n">
         <v>-0.4931</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1776</v>
+        <v>-0.1836</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1699</v>
+        <v>-0.1576</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7377</v>
+        <v>-0.6538</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4594</v>
+        <v>-0.4934</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5425</v>
+        <v>1.5479</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4498</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7362</v>
+        <v>-1.529</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0501</v>
+        <v>0.1509</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7863</v>
+        <v>-1.6799</v>
       </c>
       <c r="G20" t="n">
-        <v>0.039</v>
+        <v>0.0366</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3608</v>
+        <v>-0.3564</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3998</v>
+        <v>0.393</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1612</v>
+        <v>0.1508</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1439</v>
+        <v>0.1336</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1222</v>
+        <v>-0.1143</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3215</v>
+        <v>-0.1103</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1605</v>
+        <v>-2.0399</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6151</v>
+        <v>-1.4088</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5453</v>
+        <v>-0.6312</v>
       </c>
       <c r="G21" t="n">
-        <v>0.019</v>
+        <v>0.2769</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4588</v>
+        <v>-1.1264</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4398</v>
+        <v>1.4034</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3024</v>
+        <v>0.5356</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9395</v>
+        <v>-0.1346</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6371</v>
+        <v>0.6703</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2834</v>
+        <v>-0.2587</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4807</v>
+        <v>-0.9918</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1973</v>
+        <v>0.7331</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8184</v>
+        <v>-1.1787</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5565</v>
+        <v>-0.5786</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2619</v>
+        <v>-0.6002</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2581</v>
+        <v>-2.1678</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5132</v>
+        <v>-0.5151</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7448</v>
+        <v>-1.6527</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2622</v>
+        <v>0.0271</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1372</v>
+        <v>0.4649</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3994</v>
+        <v>-0.4379</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5434</v>
+        <v>1.2898</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1283</v>
+        <v>1.9305</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6717</v>
+        <v>-0.6407</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2812</v>
+        <v>-1.2628</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0089</v>
+        <v>-1.4656</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7277</v>
+        <v>0.2028</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3861</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6956</v>
+        <v>-0.4392</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6905</v>
+        <v>-0.3899</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6282</v>
+        <v>-4.2284</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6031</v>
+        <v>-3.3978</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0251</v>
+        <v>-0.8305</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9924</v>
+        <v>-1.9765</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5095</v>
+        <v>-2.4965</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5171</v>
+        <v>0.52</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3145</v>
+        <v>-1.3326</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1225</v>
+        <v>-1.1311</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.6439</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.387</v>
+        <v>-1.3654</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2748</v>
+        <v>-0.886</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8861</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3887</v>
+        <v>-0.2353</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8523</v>
+        <v>-5.1265</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2257</v>
+        <v>-5.619</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3734</v>
+        <v>0.4925</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.9462</v>
+        <v>-5.9638</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.0936</v>
+        <v>-4.0982</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8526</v>
+        <v>-1.8656</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.2651</v>
+        <v>-5.3051</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.2738</v>
+        <v>-3.2932</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9913</v>
+        <v>-2.0119</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6812</v>
+        <v>-0.6587</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0402</v>
+        <v>-0.3009</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0393</v>
+        <v>-0.3139</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0796</v>
+        <v>0.013</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.451600000000001</v>
+        <v>2.456700000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.455499999999999</v>
+        <v>-5.757300000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>7.907200000000001</v>
+        <v>8.214200000000002</v>
       </c>
       <c r="G25" t="n">
-        <v>12.4252</v>
+        <v>12.4554</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9369999999999985</v>
+        <v>1.001799999999998</v>
       </c>
       <c r="I25" t="n">
-        <v>11.4882</v>
+        <v>11.4536</v>
       </c>
       <c r="J25" t="n">
-        <v>14.1708</v>
+        <v>13.9555</v>
       </c>
       <c r="K25" t="n">
-        <v>8.587400000000002</v>
+        <v>8.4786</v>
       </c>
       <c r="L25" t="n">
-        <v>5.5835</v>
+        <v>5.476999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7457</v>
+        <v>-1.5005</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.650299999999999</v>
+        <v>-7.4769</v>
       </c>
       <c r="O25" t="n">
-        <v>5.904700000000001</v>
+        <v>5.976299999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.536599999999999</v>
+        <v>-4.5527</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.1466</v>
+        <v>-18.2105</v>
       </c>
       <c r="R25" t="n">
-        <v>13.6101</v>
+        <v>13.6579</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.0225</v>
+        <v>-4.040900000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.8541</v>
+        <v>-4.8573</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8316</v>
+        <v>0.8165000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W25" t="n">
-        <v>3.3746</v>
+        <v>3.3548</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.7887</v>
+        <v>-4.7599</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104598_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104598_W16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-3.3548</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104598_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-4.7599</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
